--- a/Documents/Data Science and Analytics Section Work Plan_v1.xlsx
+++ b/Documents/Data Science and Analytics Section Work Plan_v1.xlsx
@@ -2095,9 +2095,6 @@
     <t>Link to the functions</t>
   </si>
   <si>
-    <t xml:space="preserve">Data governance frame+F20:R20work developed </t>
-  </si>
-  <si>
     <t>(i) Assist in formulation, implementation, and review of policies, strategies, and guidelines on data analytics
 (ii) Collect, analyze, and interpret biological and health science data
 (iii) Support in design, development, and reporting of research studies
@@ -2109,6 +2106,9 @@
 (xii–xiv) Manage genomic/proteomic and scientific data, maintain knowledge, prepare reports
 (xviii) Analyze large amounts of information to discover trends and patterns
 (xix) Conduct capacity building and mentorships in biostatistics and modeling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data governance framework developed </t>
   </si>
 </sst>
 </file>
@@ -9884,7 +9884,7 @@
       <c r="Y11" s="42"/>
       <c r="Z11" s="43"/>
     </row>
-    <row r="12" spans="2:27" ht="53.4" thickBot="1">
+    <row r="12" spans="2:27" ht="40.200000000000003" thickBot="1">
       <c r="B12" s="30"/>
       <c r="C12" s="28"/>
       <c r="D12" s="54" t="s">
@@ -10146,7 +10146,7 @@
         <v>669</v>
       </c>
       <c r="F20" s="54" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G20" s="54" t="s">
         <v>380</v>
@@ -10155,7 +10155,7 @@
         <v>670</v>
       </c>
       <c r="I20" s="66" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="J20" s="66">
         <v>1</v>
@@ -10335,7 +10335,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="25" spans="2:26" ht="40.200000000000003" thickBot="1">
+    <row r="25" spans="2:26" ht="27" thickBot="1">
       <c r="B25" s="30"/>
       <c r="C25" s="28"/>
       <c r="D25" s="54" t="s">
@@ -10417,7 +10417,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="27" spans="2:26" ht="53.4" thickBot="1">
+    <row r="27" spans="2:26" ht="40.200000000000003" thickBot="1">
       <c r="B27" s="30"/>
       <c r="C27" s="28"/>
       <c r="D27" s="54" t="s">
@@ -10703,7 +10703,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="35" spans="2:26" ht="53.4" thickBot="1">
+    <row r="35" spans="2:26" ht="40.200000000000003" thickBot="1">
       <c r="B35" s="30"/>
       <c r="C35" s="28"/>
       <c r="D35" s="54" t="s">
@@ -10863,7 +10863,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="39" spans="2:26" ht="40.200000000000003" thickBot="1">
+    <row r="39" spans="2:26" ht="27" thickBot="1">
       <c r="B39" s="30"/>
       <c r="C39" s="28"/>
       <c r="D39" s="54"/>
@@ -10958,7 +10958,7 @@
       <c r="Y41" s="42"/>
       <c r="Z41" s="43"/>
     </row>
-    <row r="42" spans="2:26" ht="304.2" thickBot="1">
+    <row r="42" spans="2:26" ht="291" thickBot="1">
       <c r="B42" s="30"/>
       <c r="C42" s="28"/>
       <c r="D42" s="54" t="s">
@@ -11524,7 +11524,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="57" spans="2:26" ht="40.200000000000003" thickBot="1">
+    <row r="57" spans="2:26" ht="27" thickBot="1">
       <c r="B57" s="58"/>
       <c r="C57" s="28"/>
       <c r="D57" s="54" t="s">
@@ -11565,7 +11565,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="58" spans="2:26" ht="79.8" thickBot="1">
+    <row r="58" spans="2:26" ht="66.599999999999994" thickBot="1">
       <c r="B58" s="58"/>
       <c r="C58" s="28"/>
       <c r="D58" s="54" t="s">
@@ -11647,7 +11647,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="60" spans="2:26" ht="53.4" thickBot="1">
+    <row r="60" spans="2:26" ht="40.200000000000003" thickBot="1">
       <c r="B60" s="58"/>
       <c r="C60" s="28"/>
       <c r="D60" s="54" t="s">
@@ -12023,7 +12023,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="70" spans="2:26" ht="40.200000000000003" thickBot="1">
+    <row r="70" spans="2:26" ht="27" thickBot="1">
       <c r="B70" s="58"/>
       <c r="C70" s="28"/>
       <c r="D70" s="3" t="s">
@@ -12187,7 +12187,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="74" spans="2:26" ht="40.200000000000003" thickBot="1">
+    <row r="74" spans="2:26" ht="27" thickBot="1">
       <c r="B74" s="58"/>
       <c r="C74" s="28"/>
       <c r="D74" s="54" t="s">
@@ -12228,7 +12228,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="75" spans="2:26" ht="79.8" thickBot="1">
+    <row r="75" spans="2:26" ht="66.599999999999994" thickBot="1">
       <c r="B75" s="58"/>
       <c r="C75" s="28"/>
       <c r="D75" s="54" t="s">
